--- a/서버정보/20260708_리소스배포_테스트.xlsx
+++ b/서버정보/20260708_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63247E9C-2407-4AD1-B981-4D5CFA2E96E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B15DF9-EE12-4EDE-98A3-2A94134C8C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4764" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4764" uniqueCount="626">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3935,10 +3935,6 @@
   </si>
   <si>
     <t>hazr-t-dtg-bbigeoap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Noe</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4439,7 +4435,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4782,10 +4778,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -18639,10 +18632,10 @@
       <c r="B74" s="107" t="s">
         <v>182</v>
       </c>
-      <c r="C74" s="114" t="s">
+      <c r="C74" s="107" t="s">
         <v>619</v>
       </c>
-      <c r="D74" s="114" t="s">
+      <c r="D74" s="107" t="s">
         <v>383</v>
       </c>
       <c r="E74" s="107" t="s">
@@ -18675,7 +18668,7 @@
       <c r="N74" s="112" t="s">
         <v>618</v>
       </c>
-      <c r="O74" s="114" t="str">
+      <c r="O74" s="107" t="str">
         <f>SUBSTITUTE(F74,"hazr-","")&amp;"-osdisk"</f>
         <v>t-dtg-bbigeoap01-osdisk</v>
       </c>
@@ -18685,10 +18678,10 @@
       <c r="Q74" s="107" t="s">
         <v>181</v>
       </c>
-      <c r="R74" s="114"/>
+      <c r="R74" s="107"/>
       <c r="S74" s="107"/>
-      <c r="T74" s="114"/>
-      <c r="U74" s="114" t="str">
+      <c r="T74" s="107"/>
+      <c r="U74" s="107" t="str">
         <f>SUBSTITUTE(F74,"hazr-","")&amp;"-nic"</f>
         <v>t-dtg-bbigeoap01-nic</v>
       </c>
@@ -22808,7 +22801,7 @@
         <v>3</v>
       </c>
       <c r="N74" s="74" t="s">
-        <v>623</v>
+        <v>194</v>
       </c>
       <c r="O74" s="74" t="s">
         <v>198</v>
@@ -26323,7 +26316,7 @@
         <v>566</v>
       </c>
       <c r="M90" s="74" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
@@ -26358,14 +26351,14 @@
         <v>613</v>
       </c>
       <c r="K91" s="73" t="str">
-        <f t="shared" ref="K91:K92" si="6">SUBSTITUTE(I91,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="K91" si="6">SUBSTITUTE(I91,"hazr-","")&amp;"-nic"</f>
         <v>t-com-esnwas01-nic</v>
       </c>
       <c r="L91" s="73" t="s">
         <v>566</v>
       </c>
       <c r="M91" s="73" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
@@ -26405,8 +26398,8 @@
       <c r="L92" s="74" t="s">
         <v>566</v>
       </c>
-      <c r="M92" s="115" t="s">
-        <v>625</v>
+      <c r="M92" s="114" t="s">
+        <v>624</v>
       </c>
     </row>
   </sheetData>
@@ -31048,7 +31041,7 @@
         <v>24</v>
       </c>
       <c r="F41" s="74" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G41" s="74" t="s">
         <v>111</v>
@@ -33803,7 +33796,7 @@
         <v>383</v>
       </c>
       <c r="E84" s="74" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F84" s="74" t="str">
         <f t="shared" ref="F84" si="4">SUBSTITUTE(E84, "hazr-", "")&amp;"-pb"&amp;H84</f>
@@ -33835,7 +33828,7 @@
         <v>383</v>
       </c>
       <c r="E85" s="74" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F85" s="74" t="str">
         <f t="shared" ref="F85" si="5">SUBSTITUTE(E85, "hazr-", "")&amp;"-pb"&amp;H85</f>
@@ -33862,6 +33855,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34005,22 +34013,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34036,28 +34053,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/서버정보/20260708_리소스배포_테스트.xlsx
+++ b/서버정보/20260708_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B15DF9-EE12-4EDE-98A3-2A94134C8C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66F7EB3-9DF9-4AE9-9F50-BCD43E382792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4764" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4765" uniqueCount="626">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -26365,12 +26365,11 @@
       <c r="B92" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="C92" s="82" t="str" cm="1">
-        <f t="array" ref="C92">UPPER(INDEX(_xlfn.TEXTSPLIT($D92, "-"), 3))</f>
-        <v>COM</v>
+      <c r="C92" s="82" t="s">
+        <v>619</v>
       </c>
       <c r="D92" s="82" t="s">
-        <v>613</v>
+        <v>383</v>
       </c>
       <c r="E92" s="82" t="str">
         <f t="shared" ref="E92" si="7">SUBSTITUTE(I92,"hazr-","")&amp;"-nsg"</f>
@@ -33855,21 +33854,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34013,31 +33997,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34053,4 +34028,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/서버정보/20260708_리소스배포_테스트.xlsx
+++ b/서버정보/20260708_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66F7EB3-9DF9-4AE9-9F50-BCD43E382792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0991DD-E1F9-4E85-9F12-D6FAC9D87D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -11768,15 +11768,15 @@
         <v>383</v>
       </c>
       <c r="D84" s="74" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E84" s="74" t="str">
         <f t="shared" ref="E84" si="18">SUBSTITUTE(D84, "hazr-", "")&amp;"-rule"&amp;N84</f>
-        <v>t-dtg-bbigeoap01-rule8089</v>
+        <v>t-dtg-bbigeoap-lb-rule8089</v>
       </c>
       <c r="F84" s="74" t="str">
         <f t="shared" ref="F84" si="19">SUBSTITUTE(D84, "hazr-", "")&amp;"-fe"</f>
-        <v>t-dtg-bbigeoap01-fe</v>
+        <v>t-dtg-bbigeoap-lb-fe</v>
       </c>
       <c r="G84" s="74" t="s">
         <v>57</v>
@@ -11789,14 +11789,14 @@
       </c>
       <c r="J84" s="74" t="str">
         <f t="shared" ref="J84" si="20">SUBSTITUTE(D84, "hazr-", "")&amp;"-bp"</f>
-        <v>t-dtg-bbigeoap01-bp</v>
+        <v>t-dtg-bbigeoap-lb-bp</v>
       </c>
       <c r="K84" s="74">
         <v>8089</v>
       </c>
       <c r="L84" s="74" t="str">
         <f t="shared" ref="L84" si="21">SUBSTITUTE(D84, "hazr-", "")&amp;"-pb"&amp;IF(N84="", "", N84)</f>
-        <v>t-dtg-bbigeoap01-pb8089</v>
+        <v>t-dtg-bbigeoap-lb-pb8089</v>
       </c>
       <c r="M84" s="74" t="s">
         <v>57</v>
@@ -11829,15 +11829,15 @@
         <v>383</v>
       </c>
       <c r="D85" s="74" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E85" s="74" t="str">
         <f t="shared" ref="E85" si="22">SUBSTITUTE(D85, "hazr-", "")&amp;"-rule"&amp;N85</f>
-        <v>t-dtg-bbigeoap01-rule9089</v>
+        <v>t-dtg-bbigeoap-lb-rule9089</v>
       </c>
       <c r="F85" s="74" t="str">
         <f t="shared" ref="F85" si="23">SUBSTITUTE(D85, "hazr-", "")&amp;"-fe"</f>
-        <v>t-dtg-bbigeoap01-fe</v>
+        <v>t-dtg-bbigeoap-lb-fe</v>
       </c>
       <c r="G85" s="74" t="s">
         <v>57</v>
@@ -11850,14 +11850,14 @@
       </c>
       <c r="J85" s="74" t="str">
         <f t="shared" ref="J85" si="24">SUBSTITUTE(D85, "hazr-", "")&amp;"-bp"</f>
-        <v>t-dtg-bbigeoap01-bp</v>
+        <v>t-dtg-bbigeoap-lb-bp</v>
       </c>
       <c r="K85" s="74">
         <v>9089</v>
       </c>
       <c r="L85" s="74" t="str">
         <f t="shared" ref="L85" si="25">SUBSTITUTE(D85, "hazr-", "")&amp;"-pb"&amp;IF(N85="", "", N85)</f>
-        <v>t-dtg-bbigeoap01-pb9089</v>
+        <v>t-dtg-bbigeoap-lb-pb9089</v>
       </c>
       <c r="M85" s="74" t="s">
         <v>57</v>
@@ -33854,6 +33854,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -33997,22 +34012,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34028,28 +34052,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>